--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,6 +61,15 @@
     <t>2026-05-08</t>
   </si>
   <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
     <t>ДЛ3</t>
   </si>
   <si>
@@ -67,7 +79,25 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>13:14</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:13:00</t>
+  </si>
+  <si>
+    <t>09:14:00</t>
+  </si>
+  <si>
+    <t>08:58:00</t>
+  </si>
+  <si>
+    <t>3231567888 3231567888</t>
+  </si>
+  <si>
+    <t>3232017528 3232017528</t>
+  </si>
+  <si>
+    <t>3232303147 3232303147</t>
   </si>
   <si>
     <t>Общи литри по продукт / АДИГА ЕООД</t>
@@ -491,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -500,16 +530,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -549,119 +580,213 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1199</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>39.6</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
         <v>1.65</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>65.34</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.79</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>70.88</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>39.77</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
+        <v>1.63</v>
+      </c>
+      <c r="I3" s="1">
+        <v>64.83</v>
+      </c>
+      <c r="J3">
+        <v>1.76</v>
+      </c>
+      <c r="K3" s="1">
+        <v>70</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>265208</v>
+      <c r="N3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>45.98</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4">
+        <v>1.61</v>
+      </c>
+      <c r="I4" s="1">
+        <v>74.03</v>
+      </c>
+      <c r="J4">
+        <v>1.74</v>
+      </c>
+      <c r="K4" s="1">
+        <v>80.01000000000001</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="7" spans="1:14">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
+      <c r="B9" s="6">
+        <v>125.35</v>
+      </c>
+      <c r="C9" s="6">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.629</v>
+      </c>
+      <c r="E9" s="6">
+        <v>204.2</v>
+      </c>
+      <c r="F9" s="6">
+        <v>220.89</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6">
-        <v>39.6</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1.65</v>
-      </c>
-      <c r="E7" s="6">
-        <v>65.34</v>
-      </c>
-      <c r="F7" s="6">
-        <v>70.88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="9">
-        <v>39.6</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9">
-        <v>65.34</v>
-      </c>
-      <c r="F8" s="9">
-        <v>70.88</v>
+    <row r="10" spans="1:14">
+      <c r="A10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="9">
+        <v>125.35</v>
+      </c>
+      <c r="C10" s="9">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="9">
+        <v>204.2</v>
+      </c>
+      <c r="F10" s="9">
+        <v>220.89</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
@@ -151,7 +151,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,12 +161,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -216,17 +210,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,25 +46,19 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>2026-05-23</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>Варна</t>
   </si>
   <si>
     <t>ДЛ3</t>
@@ -77,27 +68,6 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>13:13:00</t>
-  </si>
-  <si>
-    <t>09:14:00</t>
-  </si>
-  <si>
-    <t>08:58:00</t>
-  </si>
-  <si>
-    <t>3231567888 3231567888</t>
-  </si>
-  <si>
-    <t>3232017528 3232017528</t>
-  </si>
-  <si>
-    <t>3232303147 3232303147</t>
   </si>
   <si>
     <t>Общи литри по продукт / АДИГА ЕООД</t>
@@ -515,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -524,17 +494,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -568,151 +535,115 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>36.15</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H2">
+        <v>57.48</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="J2">
+        <v>60.01</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>62.05</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H3">
+        <v>98.66</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="J3">
+        <v>103</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4">
+        <v>30.7</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H4">
+        <v>48.81</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="J4">
+        <v>50.04</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2">
-        <v>39.6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2">
-        <v>1.65</v>
-      </c>
-      <c r="I2" s="1">
-        <v>65.34</v>
-      </c>
-      <c r="J2">
-        <v>1.79</v>
-      </c>
-      <c r="K2" s="1">
-        <v>70.88</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>39.77</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>1.63</v>
-      </c>
-      <c r="I3" s="1">
-        <v>64.83</v>
-      </c>
-      <c r="J3">
-        <v>1.76</v>
-      </c>
-      <c r="K3" s="1">
-        <v>70</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>45.98</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4">
-        <v>1.61</v>
-      </c>
-      <c r="I4" s="1">
-        <v>74.03</v>
-      </c>
-      <c r="J4">
-        <v>1.74</v>
-      </c>
-      <c r="K4" s="1">
-        <v>80.01000000000001</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -720,62 +651,62 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:11">
       <c r="A8" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:11">
       <c r="A9" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B9" s="6">
-        <v>125.35</v>
+        <v>128.9</v>
       </c>
       <c r="C9" s="6">
         <v>3</v>
       </c>
       <c r="D9" s="7">
-        <v>1.629</v>
+        <v>1.59</v>
       </c>
       <c r="E9" s="6">
-        <v>204.2</v>
+        <v>204.95</v>
       </c>
       <c r="F9" s="6">
-        <v>220.89</v>
+        <v>213.05</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:11">
       <c r="A10" s="8" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B10" s="9">
-        <v>125.35</v>
+        <v>128.9</v>
       </c>
       <c r="C10" s="9">
         <v>3</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="9">
-        <v>204.2</v>
+        <v>204.95</v>
       </c>
       <c r="F10" s="9">
-        <v>220.89</v>
+        <v>213.05</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="44">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-04</t>
   </si>
   <si>
@@ -64,7 +73,10 @@
     <t>2026-06-24</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>ДЛ3</t>
@@ -79,19 +91,43 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-04 13:19:34</t>
-  </si>
-  <si>
-    <t>2026-06-05 14:10:28</t>
-  </si>
-  <si>
-    <t>2026-06-10 10:45:49</t>
-  </si>
-  <si>
-    <t>2026-06-16 08:59:11</t>
-  </si>
-  <si>
-    <t>2026-06-24 08:47:20</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:19:00</t>
+  </si>
+  <si>
+    <t>14:11:00</t>
+  </si>
+  <si>
+    <t>10:46:00</t>
+  </si>
+  <si>
+    <t>08:59:00</t>
+  </si>
+  <si>
+    <t>08:46:00</t>
+  </si>
+  <si>
+    <t>10:39:00</t>
+  </si>
+  <si>
+    <t>3232864835 3232864835</t>
+  </si>
+  <si>
+    <t>3232920255 3232920255</t>
+  </si>
+  <si>
+    <t>3233155230 3233155230</t>
+  </si>
+  <si>
+    <t>3233442147 3233442147</t>
+  </si>
+  <si>
+    <t>3233818731 3233818731</t>
+  </si>
+  <si>
+    <t>3234064298 3234064298</t>
   </si>
   <si>
     <t>Общи литри по продукт / АДИГА ЕООД</t>
@@ -509,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,14 +554,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -559,273 +598,371 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>36.15</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
         <v>1.56</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>56.39</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.66</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>60.01</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>62.05</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3">
         <v>1.56</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>96.8</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.66</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>103</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>30.7</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
         <v>1.53</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>46.97</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.63</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>50.04</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
       </c>
       <c r="F5">
         <v>65</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5">
         <v>1.53</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>99.45</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.59</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>103.35</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
       </c>
       <c r="F6">
         <v>49.32</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6">
         <v>1.4</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>69.05</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.51</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>74.47</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>33.13</v>
+      </c>
+      <c r="G7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="6">
-        <v>193.9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.5452</v>
-      </c>
-      <c r="E11" s="6">
-        <v>299.61</v>
-      </c>
-      <c r="F11" s="6">
-        <v>316.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="H7">
+        <v>1.42</v>
+      </c>
+      <c r="I7" s="1">
+        <v>47.04</v>
+      </c>
+      <c r="J7">
+        <v>1.51</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50.03</v>
+      </c>
+      <c r="L7" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B12" s="6">
+        <v>227.03</v>
+      </c>
+      <c r="C12" s="6">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.5269</v>
+      </c>
+      <c r="E12" s="6">
+        <v>346.65</v>
+      </c>
+      <c r="F12" s="6">
+        <v>366.43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="6">
         <v>49.32</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C13" s="6">
         <v>1</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D13" s="7">
         <v>1.4</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E13" s="6">
         <v>69.05</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F13" s="6">
         <v>74.47</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="9">
-        <v>243.22</v>
-      </c>
-      <c r="C13" s="9">
-        <v>5</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="9">
-        <v>368.66</v>
-      </c>
-      <c r="F13" s="9">
-        <v>390.87</v>
+    <row r="14" spans="1:14">
+      <c r="A14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="9">
+        <v>276.35</v>
+      </c>
+      <c r="C14" s="9">
+        <v>6</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="9">
+        <v>415.7</v>
+      </c>
+      <c r="F14" s="9">
+        <v>440.9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,13 +55,22 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-05</t>
   </si>
   <si>
     <t>2026-07-11</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>ДЛ3</t>
@@ -70,10 +82,31 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-05 09:42:35</t>
-  </si>
-  <si>
-    <t>2026-07-11 14:27:38</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:43:00</t>
+  </si>
+  <si>
+    <t>14:28:00</t>
+  </si>
+  <si>
+    <t>16:38:00</t>
+  </si>
+  <si>
+    <t>10:15:00</t>
+  </si>
+  <si>
+    <t>3234359883 3234359883</t>
+  </si>
+  <si>
+    <t>3234655841 3234655841</t>
+  </si>
+  <si>
+    <t>3235098970 3235098970</t>
+  </si>
+  <si>
+    <t>3235540083 3235540083</t>
   </si>
   <si>
     <t>Общи литри по продукт / АДИГА ЕООД</t>
@@ -491,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -500,15 +533,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -545,154 +580,260 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>61.84</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
         <v>1.43</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>88.43000000000001</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>94</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>38.93</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3">
         <v>1.46</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>56.84</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.54</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>59.95</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="L3">
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4">
+        <v>30.11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4">
+        <v>1.57</v>
+      </c>
+      <c r="I4" s="1">
+        <v>47.27</v>
+      </c>
+      <c r="J4">
+        <v>1.68</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50.58</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3" t="s">
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>28.57</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5">
+        <v>1.69</v>
+      </c>
+      <c r="I5" s="1">
+        <v>48.28</v>
+      </c>
+      <c r="J5">
+        <v>1.75</v>
+      </c>
+      <c r="K5" s="1">
+        <v>50</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:14">
+      <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
+      <c r="B10" s="6">
+        <v>159.45</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1.5103</v>
+      </c>
+      <c r="E10" s="6">
+        <v>240.82</v>
+      </c>
+      <c r="F10" s="6">
+        <v>254.53</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6">
-        <v>100.77</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.4416</v>
-      </c>
-      <c r="E8" s="6">
-        <v>145.27</v>
-      </c>
-      <c r="F8" s="6">
-        <v>153.95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="9">
-        <v>100.77</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9">
-        <v>145.27</v>
-      </c>
-      <c r="F9" s="9">
-        <v>153.95</v>
+    <row r="11" spans="1:14">
+      <c r="A11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="9">
+        <v>159.45</v>
+      </c>
+      <c r="C11" s="9">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="9">
+        <v>240.82</v>
+      </c>
+      <c r="F11" s="9">
+        <v>254.53</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
@@ -133,7 +133,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -804,7 +804,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="7">
-        <v>1.5103</v>
+        <v>1.510317</v>
       </c>
       <c r="E10" s="6">
         <v>240.82</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="38">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -524,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -537,13 +540,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -586,186 +589,201 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>61.842</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2">
+        <v>1.406</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.426</v>
+      </c>
+      <c r="J2">
+        <v>88.18669199999999</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L2" s="1">
+        <v>93.99984000000001</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>38.929</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3">
+        <v>1.437</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.457</v>
+      </c>
+      <c r="J3">
+        <v>56.719553</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L3" s="1">
+        <v>59.95066</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>30.107</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4">
+        <v>1.546</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.566</v>
+      </c>
+      <c r="J4">
+        <v>47.147562</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L4" s="1">
+        <v>50.57976</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="F2">
-        <v>61.84</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="H2">
-        <v>1.43</v>
-      </c>
-      <c r="I2" s="1">
-        <v>88.43000000000001</v>
-      </c>
-      <c r="J2">
-        <v>1.52</v>
-      </c>
-      <c r="K2" s="1">
-        <v>94</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="F5">
+        <v>28.571</v>
+      </c>
+      <c r="G5" t="s">
         <v>23</v>
       </c>
-      <c r="M2">
+      <c r="H5">
+        <v>1.674</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.694</v>
+      </c>
+      <c r="J5">
+        <v>48.399274</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L5" s="1">
+        <v>49.99925</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>27</v>
+      <c r="O5" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>38.93</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3">
-        <v>1.46</v>
-      </c>
-      <c r="I3" s="1">
-        <v>56.84</v>
-      </c>
-      <c r="J3">
-        <v>1.54</v>
-      </c>
-      <c r="K3" s="1">
-        <v>59.95</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4">
-        <v>30.11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4">
-        <v>1.57</v>
-      </c>
-      <c r="I4" s="1">
-        <v>47.27</v>
-      </c>
-      <c r="J4">
-        <v>1.68</v>
-      </c>
-      <c r="K4" s="1">
-        <v>50.58</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>28.57</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5">
-        <v>1.69</v>
-      </c>
-      <c r="I5" s="1">
-        <v>48.28</v>
-      </c>
-      <c r="J5">
-        <v>1.75</v>
-      </c>
-      <c r="K5" s="1">
-        <v>50</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -773,59 +791,59 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="6">
-        <v>159.45</v>
+        <v>159.449</v>
       </c>
       <c r="C10" s="6">
         <v>4</v>
       </c>
       <c r="D10" s="7">
-        <v>1.510317</v>
+        <v>1.508025</v>
       </c>
       <c r="E10" s="6">
-        <v>240.82</v>
+        <v>240.45</v>
       </c>
       <c r="F10" s="6">
         <v>254.53</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="9">
-        <v>159.45</v>
+        <v>159.449</v>
       </c>
       <c r="C11" s="9">
         <v>4</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="9">
-        <v>240.82</v>
+        <v>240.45</v>
       </c>
       <c r="F11" s="9">
         <v>254.53</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АДИГА ЕООД/АДИГА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -135,8 +132,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -229,10 +226,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -540,13 +537,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -589,201 +586,186 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
       </c>
       <c r="F2">
         <v>61.842</v>
       </c>
       <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
+        <v>1.426</v>
+      </c>
+      <c r="I2" s="1">
+        <v>88.187</v>
+      </c>
+      <c r="J2">
+        <v>1.52</v>
+      </c>
+      <c r="K2" s="1">
+        <v>94</v>
+      </c>
+      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="H2">
-        <v>1.406</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.426</v>
-      </c>
-      <c r="J2">
-        <v>88.18669199999999</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L2" s="1">
-        <v>93.99984000000001</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>28</v>
+      <c r="N2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
       </c>
       <c r="F3">
         <v>38.929</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3">
-        <v>1.437</v>
+        <v>1.457</v>
       </c>
       <c r="I3" s="1">
-        <v>1.457</v>
+        <v>56.72</v>
       </c>
       <c r="J3">
-        <v>56.719553</v>
+        <v>1.54</v>
       </c>
       <c r="K3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L3" s="1">
-        <v>59.95066</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3">
+        <v>59.951</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>29</v>
+      <c r="N3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
       </c>
       <c r="F4">
         <v>30.107</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4">
-        <v>1.546</v>
+        <v>1.566</v>
       </c>
       <c r="I4" s="1">
-        <v>1.566</v>
+        <v>47.148</v>
       </c>
       <c r="J4">
-        <v>47.147562</v>
+        <v>1.68</v>
       </c>
       <c r="K4" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L4" s="1">
-        <v>50.57976</v>
-      </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4">
+        <v>50.58</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>30</v>
+      <c r="N4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
       </c>
       <c r="F5">
         <v>28.571</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I5" s="1">
-        <v>1.694</v>
+        <v>48.399</v>
       </c>
       <c r="J5">
-        <v>48.399274</v>
+        <v>1.75</v>
       </c>
       <c r="K5" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L5" s="1">
-        <v>49.99925</v>
-      </c>
-      <c r="M5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5">
+        <v>49.999</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -791,49 +773,49 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="6">
         <v>159.449</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>4</v>
       </c>
       <c r="D10" s="7">
-        <v>1.508025</v>
-      </c>
-      <c r="E10" s="6">
-        <v>240.45</v>
-      </c>
-      <c r="F10" s="6">
+        <v>1.508</v>
+      </c>
+      <c r="E10" s="7">
+        <v>240.454</v>
+      </c>
+      <c r="F10" s="7">
         <v>254.53</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="9">
         <v>159.449</v>
@@ -843,7 +825,7 @@
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="9">
-        <v>240.45</v>
+        <v>240.454</v>
       </c>
       <c r="F11" s="9">
         <v>254.53</v>
